--- a/transformed_transactions_1.xlsx
+++ b/transformed_transactions_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yusra Faisal\OneDrive\Desktop\sbb\social_banking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1274DF-DD88-43F4-AD36-0D0F9FE77CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA5EB9F-7A4F-44ED-8BF6-5206684A852D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="405" windowWidth="11355" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,9 +85,6 @@
     <t>Amazon</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
     <t>Shopping</t>
   </si>
   <si>
@@ -110,6 +107,9 @@
   </si>
   <si>
     <t>Travel</t>
+  </si>
+  <si>
+    <t>category</t>
   </si>
 </sst>
 </file>
@@ -518,6 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -541,7 +542,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -570,7 +571,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>5035.0600000000004</v>
@@ -599,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>8468.68</v>
@@ -628,7 +629,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>21846.67</v>
@@ -657,7 +658,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -686,7 +687,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -715,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>7537.58</v>
@@ -744,7 +745,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>17774.64</v>
@@ -773,7 +774,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9">
         <v>11122.24</v>
@@ -802,7 +803,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -831,7 +832,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -860,7 +861,7 @@
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -889,7 +890,7 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -918,7 +919,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -947,7 +948,7 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -976,7 +977,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1005,7 +1006,7 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>23710.43</v>
@@ -1034,7 +1035,7 @@
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>778.64</v>
@@ -1063,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19">
         <v>21033.35</v>
@@ -1092,7 +1093,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1121,7 +1122,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1150,7 +1151,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1179,7 +1180,7 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1208,7 +1209,7 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24">
         <v>8192.65</v>
@@ -1237,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1266,7 +1267,7 @@
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1295,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>940.15</v>
@@ -1324,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28">
         <v>24050.84</v>
@@ -1353,7 +1354,7 @@
         <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29">
         <v>21108.06</v>
@@ -1382,7 +1383,7 @@
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30">
         <v>13421.81</v>
@@ -1411,7 +1412,7 @@
         <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31">
         <v>7187.68</v>
@@ -1426,7 +1427,7 @@
         <v>142805.9500000001</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1002</v>
       </c>
@@ -1440,7 +1441,7 @@
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1455,7 +1456,7 @@
         <v>39992.920000000013</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1002</v>
       </c>
@@ -1469,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <v>9473.27</v>
@@ -1484,7 +1485,7 @@
         <v>87008.63</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1002</v>
       </c>
@@ -1498,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F34">
         <v>3654.59</v>
@@ -1513,7 +1514,7 @@
         <v>121171.87</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -1527,7 +1528,7 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1542,7 +1543,7 @@
         <v>102381.32</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1002</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1571,7 +1572,7 @@
         <v>205077.78000000009</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1002</v>
       </c>
@@ -1585,7 +1586,7 @@
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1600,7 +1601,7 @@
         <v>286452.39</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1002</v>
       </c>
@@ -1614,7 +1615,7 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38">
         <v>23955.94</v>
@@ -1629,7 +1630,7 @@
         <v>286452.39</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1002</v>
       </c>
@@ -1643,7 +1644,7 @@
         <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>23899.19</v>
@@ -1658,7 +1659,7 @@
         <v>310766.87</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1002</v>
       </c>
@@ -1672,7 +1673,7 @@
         <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1687,7 +1688,7 @@
         <v>316522.78999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1002</v>
       </c>
@@ -1701,7 +1702,7 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F41">
         <v>17456.95</v>
@@ -1716,7 +1717,7 @@
         <v>321403.08</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1002</v>
       </c>
@@ -1730,7 +1731,7 @@
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F42">
         <v>9673.66</v>
@@ -1745,7 +1746,7 @@
         <v>322189.03999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1002</v>
       </c>
@@ -1759,7 +1760,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1774,7 +1775,7 @@
         <v>281411.52</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1002</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1803,7 +1804,7 @@
         <v>310935.42999999988</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1002</v>
       </c>
@@ -1817,7 +1818,7 @@
         <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -1832,7 +1833,7 @@
         <v>305156.60999999993</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1002</v>
       </c>
@@ -1846,7 +1847,7 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F46">
         <v>1379.3</v>
@@ -1861,7 +1862,7 @@
         <v>320703.22999999992</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1002</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1890,7 +1891,7 @@
         <v>313589.22999999992</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1002</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F48">
         <v>21566.79</v>
@@ -1919,7 +1920,7 @@
         <v>282870.21999999991</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1002</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -1948,7 +1949,7 @@
         <v>298447.31999999989</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1002</v>
       </c>
@@ -1962,7 +1963,7 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1977,7 +1978,7 @@
         <v>267322.73</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1002</v>
       </c>
@@ -1991,7 +1992,7 @@
         <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F51">
         <v>11483.42</v>
@@ -2006,7 +2007,7 @@
         <v>160444.34</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1002</v>
       </c>
@@ -2020,7 +2021,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F52">
         <v>15975.45</v>
@@ -2035,7 +2036,7 @@
         <v>160444.34</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1002</v>
       </c>
@@ -2049,7 +2050,7 @@
         <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F53">
         <v>16987.240000000002</v>
@@ -2064,7 +2065,7 @@
         <v>160444.34</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1002</v>
       </c>
@@ -2078,7 +2079,7 @@
         <v>14</v>
       </c>
       <c r="E54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F54">
         <v>17068.75</v>
@@ -2093,7 +2094,7 @@
         <v>160444.34</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1002</v>
       </c>
@@ -2107,7 +2108,7 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2122,7 +2123,7 @@
         <v>152303.12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1002</v>
       </c>
@@ -2136,7 +2137,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56">
         <v>1485.36</v>
@@ -2151,7 +2152,7 @@
         <v>154137.14000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1002</v>
       </c>
@@ -2165,7 +2166,7 @@
         <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F57">
         <v>16596.099999999999</v>
@@ -2180,7 +2181,7 @@
         <v>154137.14000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1002</v>
       </c>
@@ -2194,7 +2195,7 @@
         <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F58">
         <v>593.08000000000004</v>
@@ -2209,7 +2210,7 @@
         <v>147587.72000000009</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1002</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>17</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2238,7 +2239,7 @@
         <v>165512.03000000009</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1002</v>
       </c>
@@ -2252,7 +2253,7 @@
         <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F60">
         <v>10599.13</v>
@@ -2267,7 +2268,7 @@
         <v>165512.03000000009</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1002</v>
       </c>
@@ -2281,7 +2282,7 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2296,7 +2297,7 @@
         <v>142805.9500000001</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1003</v>
       </c>
@@ -2310,7 +2311,7 @@
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F62">
         <v>9082.74</v>
@@ -2325,7 +2326,7 @@
         <v>24519.439999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1003</v>
       </c>
@@ -2339,7 +2340,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2354,7 +2355,7 @@
         <v>28477.439999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1003</v>
       </c>
@@ -2368,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2383,7 +2384,7 @@
         <v>15385.39</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1003</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>17</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2412,7 +2413,7 @@
         <v>40293.58</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1003</v>
       </c>
@@ -2426,7 +2427,7 @@
         <v>14</v>
       </c>
       <c r="E66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2441,7 +2442,7 @@
         <v>55006.62000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1003</v>
       </c>
@@ -2455,7 +2456,7 @@
         <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -2470,7 +2471,7 @@
         <v>80902.360000000015</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1003</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2499,7 +2500,7 @@
         <v>100276.29</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1003</v>
       </c>
@@ -2513,7 +2514,7 @@
         <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2528,7 +2529,7 @@
         <v>127392.51</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1003</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>17</v>
       </c>
       <c r="E70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2557,7 +2558,7 @@
         <v>138839.71</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1003</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F71">
         <v>16583.66</v>
@@ -2586,7 +2587,7 @@
         <v>138839.71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1003</v>
       </c>
@@ -2600,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F72">
         <v>17527.29</v>
@@ -2615,7 +2616,7 @@
         <v>138839.71</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1003</v>
       </c>
@@ -2629,7 +2630,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F73">
         <v>2607.7199999999998</v>
@@ -2644,7 +2645,7 @@
         <v>310766.87</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1003</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F74">
         <v>20459.11</v>
@@ -2673,7 +2674,7 @@
         <v>321403.08</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1003</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F75">
         <v>24080.86</v>
@@ -2702,7 +2703,7 @@
         <v>326280.03999999992</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -2716,7 +2717,7 @@
         <v>16</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F76">
         <v>2905.07</v>
@@ -2731,7 +2732,7 @@
         <v>289776.53999999992</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1003</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>17</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77">
         <v>9792.89</v>
@@ -2760,7 +2761,7 @@
         <v>291634.41999999993</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1003</v>
       </c>
@@ -2774,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2789,7 +2790,7 @@
         <v>282870.21999999991</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1003</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F79">
         <v>21428.959999999999</v>
@@ -2818,7 +2819,7 @@
         <v>287489.4499999999</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1003</v>
       </c>
@@ -2832,7 +2833,7 @@
         <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F80">
         <v>12978.24</v>
@@ -2847,7 +2848,7 @@
         <v>287489.4499999999</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1003</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F81">
         <v>12904.79</v>
@@ -2876,7 +2877,7 @@
         <v>298472.87999999989</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1003</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>17</v>
       </c>
       <c r="E82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F82">
         <v>19364.23</v>
@@ -2905,7 +2906,7 @@
         <v>230392.75</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1003</v>
       </c>
@@ -2919,7 +2920,7 @@
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2934,7 +2935,7 @@
         <v>160444.34</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1003</v>
       </c>
@@ -2948,7 +2949,7 @@
         <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -2963,7 +2964,7 @@
         <v>152729.51999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1003</v>
       </c>
@@ -2977,7 +2978,7 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -2992,7 +2993,7 @@
         <v>164822.31000000011</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1003</v>
       </c>
@@ -3006,7 +3007,7 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F86">
         <v>3402.96</v>
@@ -3021,7 +3022,7 @@
         <v>164822.31000000011</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1003</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F87">
         <v>23279.21</v>
@@ -3050,7 +3051,7 @@
         <v>170269.24</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1003</v>
       </c>
@@ -3064,7 +3065,7 @@
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F88">
         <v>15586.42</v>
@@ -3079,7 +3080,7 @@
         <v>147587.72000000009</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1003</v>
       </c>
@@ -3093,7 +3094,7 @@
         <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3108,7 +3109,7 @@
         <v>163000.3600000001</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1003</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -3137,7 +3138,7 @@
         <v>181159.96000000011</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1003</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F91">
         <v>5487.81</v>
@@ -3166,7 +3167,7 @@
         <v>192562.99</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1004</v>
       </c>
@@ -3180,7 +3181,7 @@
         <v>15</v>
       </c>
       <c r="E92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F92">
         <v>13094</v>
@@ -3195,7 +3196,7 @@
         <v>79983.790000000008</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1004</v>
       </c>
@@ -3209,7 +3210,7 @@
         <v>15</v>
       </c>
       <c r="E93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -3224,7 +3225,7 @@
         <v>81025.87000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1004</v>
       </c>
@@ -3238,7 +3239,7 @@
         <v>17</v>
       </c>
       <c r="E94" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -3253,7 +3254,7 @@
         <v>87008.63</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1004</v>
       </c>
@@ -3267,7 +3268,7 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -3282,7 +3283,7 @@
         <v>121171.87</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1004</v>
       </c>
@@ -3296,7 +3297,7 @@
         <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -3311,7 +3312,7 @@
         <v>122444.24</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1004</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -3340,7 +3341,7 @@
         <v>116293.45</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1004</v>
       </c>
@@ -3354,7 +3355,7 @@
         <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -3369,7 +3370,7 @@
         <v>129367.63</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1004</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="E99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F99">
         <v>4373.4399999999996</v>
@@ -3398,7 +3399,7 @@
         <v>129367.63</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1004</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F100">
         <v>2269.67</v>
@@ -3427,7 +3428,7 @@
         <v>129367.63</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1004</v>
       </c>
@@ -3441,7 +3442,7 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -3456,7 +3457,7 @@
         <v>251819.21000000011</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1004</v>
       </c>
@@ -3470,7 +3471,7 @@
         <v>17</v>
       </c>
       <c r="E102" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -3485,7 +3486,7 @@
         <v>269587.78000000003</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1004</v>
       </c>
@@ -3499,7 +3500,7 @@
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F103">
         <v>11103.59</v>
@@ -3514,7 +3515,7 @@
         <v>278499.28000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1004</v>
       </c>
@@ -3528,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="E104" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -3543,7 +3544,7 @@
         <v>271619.19</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1004</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>17</v>
       </c>
       <c r="E105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3572,7 +3573,7 @@
         <v>310766.87</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1004</v>
       </c>
@@ -3586,7 +3587,7 @@
         <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F106">
         <v>24792.47</v>
@@ -3601,7 +3602,7 @@
         <v>303059.46999999997</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1004</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3630,7 +3631,7 @@
         <v>283071.08</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1004</v>
       </c>
@@ -3644,7 +3645,7 @@
         <v>15</v>
       </c>
       <c r="E108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F108">
         <v>7720.55</v>
@@ -3659,7 +3660,7 @@
         <v>320759.11</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1004</v>
       </c>
@@ -3673,7 +3674,7 @@
         <v>16</v>
       </c>
       <c r="E109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -3688,7 +3689,7 @@
         <v>289776.53999999992</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1004</v>
       </c>
@@ -3702,7 +3703,7 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3717,7 +3718,7 @@
         <v>279328.85999999993</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1004</v>
       </c>
@@ -3731,7 +3732,7 @@
         <v>13</v>
       </c>
       <c r="E111" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F111">
         <v>9164.4699999999993</v>
@@ -3746,7 +3747,7 @@
         <v>282870.21999999991</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1004</v>
       </c>
@@ -3760,7 +3761,7 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F112">
         <v>784.69</v>
@@ -3775,7 +3776,7 @@
         <v>298472.87999999989</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1004</v>
       </c>
@@ -3789,7 +3790,7 @@
         <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3804,7 +3805,7 @@
         <v>288246.2099999999</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1004</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>16</v>
       </c>
       <c r="E114" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F114">
         <v>1060.97</v>
@@ -3833,7 +3834,7 @@
         <v>274424.47999999992</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1004</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>16</v>
       </c>
       <c r="E115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F115">
         <v>17280.5</v>
@@ -3862,7 +3863,7 @@
         <v>279195.95</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1004</v>
       </c>
@@ -3876,7 +3877,7 @@
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -3891,7 +3892,7 @@
         <v>299242.35999999993</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1004</v>
       </c>
@@ -3905,7 +3906,7 @@
         <v>16</v>
       </c>
       <c r="E117" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F117">
         <v>17708.93</v>
@@ -3920,7 +3921,7 @@
         <v>164822.31000000011</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1004</v>
       </c>
@@ -3934,7 +3935,7 @@
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3949,7 +3950,7 @@
         <v>171976.61</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1004</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v>19</v>
       </c>
       <c r="E119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F119">
         <v>10595.74</v>
@@ -3978,7 +3979,7 @@
         <v>181159.96000000011</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1004</v>
       </c>
@@ -3992,7 +3993,7 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -4007,7 +4008,7 @@
         <v>158824.94</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1004</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -4036,7 +4037,7 @@
         <v>179325.41</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1005</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>17</v>
       </c>
       <c r="E122" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -4065,7 +4066,7 @@
         <v>52199.09</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>1005</v>
       </c>
@@ -4079,7 +4080,7 @@
         <v>16</v>
       </c>
       <c r="E123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F123">
         <v>6457.05</v>
@@ -4094,7 +4095,7 @@
         <v>79983.790000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>1005</v>
       </c>
@@ -4108,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F124">
         <v>21844.19</v>
@@ -4123,7 +4124,7 @@
         <v>87008.63</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>1005</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>16</v>
       </c>
       <c r="E125" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F125">
         <v>4763.0600000000004</v>
@@ -4152,7 +4153,7 @@
         <v>121171.87</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>1005</v>
       </c>
@@ -4166,7 +4167,7 @@
         <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F126">
         <v>24796.73</v>
@@ -4181,7 +4182,7 @@
         <v>140463.6</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>1005</v>
       </c>
@@ -4195,7 +4196,7 @@
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F127">
         <v>19731.11</v>
@@ -4210,7 +4211,7 @@
         <v>140463.6</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>1005</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -4239,7 +4240,7 @@
         <v>280833.59000000003</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>1005</v>
       </c>
@@ -4253,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="E129" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F129">
         <v>11310.98</v>
@@ -4268,7 +4269,7 @@
         <v>276031.82</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>1005</v>
       </c>
@@ -4282,7 +4283,7 @@
         <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F130">
         <v>16554.75</v>
@@ -4297,7 +4298,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>1005</v>
       </c>
@@ -4311,7 +4312,7 @@
         <v>12</v>
       </c>
       <c r="E131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -4326,7 +4327,7 @@
         <v>326280.03999999992</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>1005</v>
       </c>
@@ -4340,7 +4341,7 @@
         <v>13</v>
       </c>
       <c r="E132" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F132">
         <v>21073.73</v>
@@ -4355,7 +4356,7 @@
         <v>289776.53999999992</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>1005</v>
       </c>
@@ -4369,7 +4370,7 @@
         <v>18</v>
       </c>
       <c r="E133" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -4384,7 +4385,7 @@
         <v>291634.41999999993</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>1005</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>17</v>
       </c>
       <c r="E134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -4413,7 +4414,7 @@
         <v>287489.4499999999</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>1005</v>
       </c>
@@ -4427,7 +4428,7 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F135">
         <v>20001.34</v>
@@ -4442,7 +4443,7 @@
         <v>279195.95</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>1005</v>
       </c>
@@ -4456,7 +4457,7 @@
         <v>19</v>
       </c>
       <c r="E136" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F136">
         <v>1740.87</v>
@@ -4471,7 +4472,7 @@
         <v>267322.73</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1005</v>
       </c>
@@ -4485,7 +4486,7 @@
         <v>17</v>
       </c>
       <c r="E137" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F137">
         <v>23098.83</v>
@@ -4500,7 +4501,7 @@
         <v>165202.6</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1005</v>
       </c>
@@ -4514,7 +4515,7 @@
         <v>12</v>
       </c>
       <c r="E138" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F138">
         <v>16300.83</v>
@@ -4529,7 +4530,7 @@
         <v>160444.34</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1005</v>
       </c>
@@ -4543,7 +4544,7 @@
         <v>17</v>
       </c>
       <c r="E139" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -4558,7 +4559,7 @@
         <v>169196.54</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1005</v>
       </c>
@@ -4572,7 +4573,7 @@
         <v>19</v>
       </c>
       <c r="E140" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F140">
         <v>15161.01</v>
@@ -4587,7 +4588,7 @@
         <v>169196.54</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1005</v>
       </c>
@@ -4601,7 +4602,7 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F141">
         <v>24081.7</v>
@@ -4616,7 +4617,7 @@
         <v>169196.54</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>1005</v>
       </c>
@@ -4630,7 +4631,7 @@
         <v>15</v>
       </c>
       <c r="E142" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F142">
         <v>11337.96</v>
@@ -4645,7 +4646,7 @@
         <v>164822.31000000011</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>1005</v>
       </c>
@@ -4659,7 +4660,7 @@
         <v>15</v>
       </c>
       <c r="E143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F143">
         <v>9695.5499999999993</v>
@@ -4674,7 +4675,7 @@
         <v>164822.31000000011</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>1005</v>
       </c>
@@ -4688,7 +4689,7 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -4703,7 +4704,7 @@
         <v>177837.53</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>1005</v>
       </c>
@@ -4717,7 +4718,7 @@
         <v>13</v>
       </c>
       <c r="E145" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F145">
         <v>7142.9</v>
@@ -4732,7 +4733,7 @@
         <v>177837.53</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1005</v>
       </c>
@@ -4746,7 +4747,7 @@
         <v>15</v>
       </c>
       <c r="E146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -4761,7 +4762,7 @@
         <v>175477.13</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>1005</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>16</v>
       </c>
       <c r="E147" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -4790,7 +4791,7 @@
         <v>200088.28</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1005</v>
       </c>
@@ -4804,7 +4805,7 @@
         <v>15</v>
       </c>
       <c r="E148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F148">
         <v>9329.41</v>
@@ -4819,7 +4820,7 @@
         <v>200088.28</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1005</v>
       </c>
@@ -4833,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="E149" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -4848,7 +4849,7 @@
         <v>181169.19</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1005</v>
       </c>
@@ -4862,7 +4863,7 @@
         <v>15</v>
       </c>
       <c r="E150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F150">
         <v>6395.93</v>
@@ -4877,7 +4878,7 @@
         <v>179325.41</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>1005</v>
       </c>
@@ -4891,7 +4892,7 @@
         <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F151">
         <v>3563.16</v>
@@ -4906,7 +4907,7 @@
         <v>179325.41</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>1006</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F152">
         <v>3680.96</v>
@@ -4935,7 +4936,7 @@
         <v>28477.439999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>1006</v>
       </c>
@@ -4949,7 +4950,7 @@
         <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -4964,7 +4965,7 @@
         <v>44138.11</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1006</v>
       </c>
@@ -4978,7 +4979,7 @@
         <v>17</v>
       </c>
       <c r="E154" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -4993,7 +4994,7 @@
         <v>77966.970000000016</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1006</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>12</v>
       </c>
       <c r="E155" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -5022,7 +5023,7 @@
         <v>272128.34999999998</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1006</v>
       </c>
@@ -5036,7 +5037,7 @@
         <v>12</v>
       </c>
       <c r="E156" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F156">
         <v>24010.83</v>
@@ -5051,7 +5052,7 @@
         <v>272128.34999999998</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1006</v>
       </c>
@@ -5065,7 +5066,7 @@
         <v>18</v>
       </c>
       <c r="E157" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F157">
         <v>14349.73</v>
@@ -5080,7 +5081,7 @@
         <v>276031.82</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1006</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>19</v>
       </c>
       <c r="E158" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -5109,7 +5110,7 @@
         <v>293876.45</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1006</v>
       </c>
@@ -5123,7 +5124,7 @@
         <v>12</v>
       </c>
       <c r="E159" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -5138,7 +5139,7 @@
         <v>306538.31</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>1006</v>
       </c>
@@ -5152,7 +5153,7 @@
         <v>18</v>
       </c>
       <c r="E160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -5167,7 +5168,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>1006</v>
       </c>
@@ -5181,7 +5182,7 @@
         <v>18</v>
       </c>
       <c r="E161" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F161">
         <v>23059.79</v>
@@ -5196,7 +5197,7 @@
         <v>320759.11</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>1006</v>
       </c>
@@ -5210,7 +5211,7 @@
         <v>12</v>
       </c>
       <c r="E162" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -5225,7 +5226,7 @@
         <v>302687.53000000003</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1006</v>
       </c>
@@ -5239,7 +5240,7 @@
         <v>19</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F163">
         <v>19110.75</v>
@@ -5254,7 +5255,7 @@
         <v>281411.52</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1006</v>
       </c>
@@ -5268,7 +5269,7 @@
         <v>10</v>
       </c>
       <c r="E164" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F164">
         <v>3767.74</v>
@@ -5283,7 +5284,7 @@
         <v>304838.21000000002</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1006</v>
       </c>
@@ -5297,7 +5298,7 @@
         <v>17</v>
       </c>
       <c r="E165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F165">
         <v>17132.77</v>
@@ -5312,7 +5313,7 @@
         <v>310935.42999999988</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>1006</v>
       </c>
@@ -5326,7 +5327,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F166">
         <v>5528.64</v>
@@ -5341,7 +5342,7 @@
         <v>320703.22999999992</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1006</v>
       </c>
@@ -5355,7 +5356,7 @@
         <v>11</v>
       </c>
       <c r="E167" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -5370,7 +5371,7 @@
         <v>309722.92999999988</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1006</v>
       </c>
@@ -5384,7 +5385,7 @@
         <v>18</v>
       </c>
       <c r="E168" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -5399,7 +5400,7 @@
         <v>308111.17999999988</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>1006</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>13</v>
       </c>
       <c r="E169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F169">
         <v>5222.79</v>
@@ -5428,7 +5429,7 @@
         <v>294364.71000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1006</v>
       </c>
@@ -5442,7 +5443,7 @@
         <v>13</v>
       </c>
       <c r="E170" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -5457,7 +5458,7 @@
         <v>283003.36</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>1006</v>
       </c>
@@ -5471,7 +5472,7 @@
         <v>12</v>
       </c>
       <c r="E171" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F171">
         <v>5789.03</v>
@@ -5486,7 +5487,7 @@
         <v>275034.07</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>1006</v>
       </c>
@@ -5500,7 +5501,7 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F172">
         <v>12371.16</v>
@@ -5515,7 +5516,7 @@
         <v>267322.73</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1006</v>
       </c>
@@ -5529,7 +5530,7 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -5544,7 +5545,7 @@
         <v>244923.83</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>1006</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="E174" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -5573,7 +5574,7 @@
         <v>153923.1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1006</v>
       </c>
@@ -5587,7 +5588,7 @@
         <v>12</v>
       </c>
       <c r="E175" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -5602,7 +5603,7 @@
         <v>154137.14000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>1006</v>
       </c>
@@ -5616,7 +5617,7 @@
         <v>12</v>
       </c>
       <c r="E176" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F176">
         <v>24758.240000000002</v>
@@ -5631,7 +5632,7 @@
         <v>201685.57</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1006</v>
       </c>
@@ -5645,7 +5646,7 @@
         <v>12</v>
       </c>
       <c r="E177" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F177">
         <v>6143.16</v>
@@ -5660,7 +5661,7 @@
         <v>201685.57</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>1006</v>
       </c>
@@ -5674,7 +5675,7 @@
         <v>19</v>
       </c>
       <c r="E178" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F178">
         <v>19609.669999999998</v>
@@ -5689,7 +5690,7 @@
         <v>201685.57</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>1006</v>
       </c>
@@ -5703,7 +5704,7 @@
         <v>17</v>
       </c>
       <c r="E179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F179">
         <v>23223.65</v>
@@ -5718,7 +5719,7 @@
         <v>201685.57</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>1006</v>
       </c>
@@ -5732,7 +5733,7 @@
         <v>13</v>
       </c>
       <c r="E180" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -5747,7 +5748,7 @@
         <v>181595.53</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>1006</v>
       </c>
@@ -5761,7 +5762,7 @@
         <v>18</v>
       </c>
       <c r="E181" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -5776,7 +5777,7 @@
         <v>192562.99</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1007</v>
       </c>
@@ -5790,7 +5791,7 @@
         <v>13</v>
       </c>
       <c r="E182" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F182">
         <v>8357.1299999999992</v>
@@ -5805,7 +5806,7 @@
         <v>28477.439999999999</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1007</v>
       </c>
@@ -5819,7 +5820,7 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -5834,7 +5835,7 @@
         <v>32525.91</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1007</v>
       </c>
@@ -5848,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="E184" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -5863,7 +5864,7 @@
         <v>76975.890000000014</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1007</v>
       </c>
@@ -5877,7 +5878,7 @@
         <v>13</v>
       </c>
       <c r="E185" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -5892,7 +5893,7 @@
         <v>169909.73</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1007</v>
       </c>
@@ -5906,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="E186" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -5921,7 +5922,7 @@
         <v>188533.95</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>1007</v>
       </c>
@@ -5935,7 +5936,7 @@
         <v>15</v>
       </c>
       <c r="E187" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F187">
         <v>6227.06</v>
@@ -5950,7 +5951,7 @@
         <v>188533.95</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>1007</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>19</v>
       </c>
       <c r="E188" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F188">
         <v>16320.19</v>
@@ -5979,7 +5980,7 @@
         <v>207459.90000000011</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>1007</v>
       </c>
@@ -5993,7 +5994,7 @@
         <v>18</v>
       </c>
       <c r="E189" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F189">
         <v>4222.8900000000003</v>
@@ -6008,7 +6009,7 @@
         <v>255362.51</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>1007</v>
       </c>
@@ -6022,7 +6023,7 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -6037,7 +6038,7 @@
         <v>278499.28000000003</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1007</v>
       </c>
@@ -6051,7 +6052,7 @@
         <v>18</v>
       </c>
       <c r="E191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F191">
         <v>2224.44</v>
@@ -6066,7 +6067,7 @@
         <v>278499.28000000003</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1007</v>
       </c>
@@ -6080,7 +6081,7 @@
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F192">
         <v>15403.76</v>
@@ -6095,7 +6096,7 @@
         <v>280833.59000000003</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1007</v>
       </c>
@@ -6109,7 +6110,7 @@
         <v>13</v>
       </c>
       <c r="E193" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -6124,7 +6125,7 @@
         <v>276031.82</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1007</v>
       </c>
@@ -6138,7 +6139,7 @@
         <v>16</v>
       </c>
       <c r="E194" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -6153,7 +6154,7 @@
         <v>302755.59000000003</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1007</v>
       </c>
@@ -6167,7 +6168,7 @@
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F195">
         <v>24938.01</v>
@@ -6182,7 +6183,7 @@
         <v>304838.21000000002</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1007</v>
       </c>
@@ -6196,7 +6197,7 @@
         <v>19</v>
       </c>
       <c r="E196" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -6211,7 +6212,7 @@
         <v>313151.81999999989</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>1007</v>
       </c>
@@ -6225,7 +6226,7 @@
         <v>15</v>
       </c>
       <c r="E197" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -6240,7 +6241,7 @@
         <v>320703.22999999992</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>1007</v>
       </c>
@@ -6254,7 +6255,7 @@
         <v>17</v>
       </c>
       <c r="E198" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -6269,7 +6270,7 @@
         <v>294364.71000000002</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>1007</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -6298,7 +6299,7 @@
         <v>155197.32</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1007</v>
       </c>
@@ -6312,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="E200" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -6327,7 +6328,7 @@
         <v>177498.22</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1007</v>
       </c>
@@ -6341,7 +6342,7 @@
         <v>18</v>
       </c>
       <c r="E201" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F201">
         <v>2442.84</v>
@@ -6356,7 +6357,7 @@
         <v>133611.4</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1007</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>18</v>
       </c>
       <c r="E202" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -6385,7 +6386,7 @@
         <v>157536.22</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1007</v>
       </c>
@@ -6399,7 +6400,7 @@
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F203">
         <v>14587.88</v>
@@ -6414,7 +6415,7 @@
         <v>157536.22</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1007</v>
       </c>
@@ -6428,7 +6429,7 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -6443,7 +6444,7 @@
         <v>154395.26</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>1007</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>17</v>
       </c>
       <c r="E205" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F205">
         <v>15933.23</v>
@@ -6472,7 +6473,7 @@
         <v>154395.26</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1007</v>
       </c>
@@ -6486,7 +6487,7 @@
         <v>10</v>
       </c>
       <c r="E206" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F206">
         <v>19858.71</v>
@@ -6501,7 +6502,7 @@
         <v>154395.26</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1007</v>
       </c>
@@ -6515,7 +6516,7 @@
         <v>15</v>
       </c>
       <c r="E207" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -6530,7 +6531,7 @@
         <v>170269.24</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>1007</v>
       </c>
@@ -6544,7 +6545,7 @@
         <v>18</v>
       </c>
       <c r="E208" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F208">
         <v>1159.3599999999999</v>
@@ -6559,7 +6560,7 @@
         <v>170269.24</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1007</v>
       </c>
@@ -6573,7 +6574,7 @@
         <v>18</v>
       </c>
       <c r="E209" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F209">
         <v>21351.57</v>
@@ -6588,7 +6589,7 @@
         <v>170269.24</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1007</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>16</v>
       </c>
       <c r="E210" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -6617,7 +6618,7 @@
         <v>179527.7600000001</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1007</v>
       </c>
@@ -6631,7 +6632,7 @@
         <v>12</v>
       </c>
       <c r="E211" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -6646,7 +6647,7 @@
         <v>201685.57</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1008</v>
       </c>
@@ -6660,7 +6661,7 @@
         <v>16</v>
       </c>
       <c r="E212" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F212">
         <v>14488.32</v>
@@ -6675,7 +6676,7 @@
         <v>32525.91</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1008</v>
       </c>
@@ -6689,7 +6690,7 @@
         <v>18</v>
       </c>
       <c r="E213" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -6704,7 +6705,7 @@
         <v>78734.960000000021</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1008</v>
       </c>
@@ -6718,7 +6719,7 @@
         <v>13</v>
       </c>
       <c r="E214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F214">
         <v>16265.82</v>
@@ -6733,7 +6734,7 @@
         <v>100276.29</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>1008</v>
       </c>
@@ -6747,7 +6748,7 @@
         <v>19</v>
       </c>
       <c r="E215" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -6762,7 +6763,7 @@
         <v>79983.790000000008</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>1008</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F216">
         <v>5721.85</v>
@@ -6791,7 +6792,7 @@
         <v>188533.95</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>1008</v>
       </c>
@@ -6805,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="E217" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -6820,7 +6821,7 @@
         <v>207459.90000000011</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1008</v>
       </c>
@@ -6834,7 +6835,7 @@
         <v>12</v>
       </c>
       <c r="E218" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -6849,7 +6850,7 @@
         <v>228091.11</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1008</v>
       </c>
@@ -6863,7 +6864,7 @@
         <v>12</v>
       </c>
       <c r="E219" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F219">
         <v>12960.24</v>
@@ -6878,7 +6879,7 @@
         <v>278499.28000000003</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1008</v>
       </c>
@@ -6892,7 +6893,7 @@
         <v>18</v>
       </c>
       <c r="E220" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F220">
         <v>7631.1</v>
@@ -6907,7 +6908,7 @@
         <v>276031.82</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1008</v>
       </c>
@@ -6921,7 +6922,7 @@
         <v>13</v>
       </c>
       <c r="E221" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F221">
         <v>7480.5</v>
@@ -6936,7 +6937,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1008</v>
       </c>
@@ -6950,7 +6951,7 @@
         <v>11</v>
       </c>
       <c r="E222" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F222">
         <v>14518.37</v>
@@ -6965,7 +6966,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1008</v>
       </c>
@@ -6979,7 +6980,7 @@
         <v>17</v>
       </c>
       <c r="E223" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F223">
         <v>7213.26</v>
@@ -6994,7 +6995,7 @@
         <v>302687.53000000003</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>1008</v>
       </c>
@@ -7008,7 +7009,7 @@
         <v>10</v>
       </c>
       <c r="E224" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F224">
         <v>18409.080000000002</v>
@@ -7023,7 +7024,7 @@
         <v>304838.21000000002</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1008</v>
       </c>
@@ -7037,7 +7038,7 @@
         <v>17</v>
       </c>
       <c r="E225" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F225">
         <v>2369.94</v>
@@ -7052,7 +7053,7 @@
         <v>304838.21000000002</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1008</v>
       </c>
@@ -7066,7 +7067,7 @@
         <v>17</v>
       </c>
       <c r="E226" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F226">
         <v>13393.05</v>
@@ -7081,7 +7082,7 @@
         <v>304838.21000000002</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1008</v>
       </c>
@@ -7095,7 +7096,7 @@
         <v>16</v>
       </c>
       <c r="E227" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F227">
         <v>16744.759999999998</v>
@@ -7110,7 +7111,7 @@
         <v>305156.60999999993</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1008</v>
       </c>
@@ -7124,7 +7125,7 @@
         <v>19</v>
       </c>
       <c r="E228" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F228">
         <v>16719.82</v>
@@ -7139,7 +7140,7 @@
         <v>305156.60999999993</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1008</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>19</v>
       </c>
       <c r="E229" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F229">
         <v>0</v>
@@ -7168,7 +7169,7 @@
         <v>330678.55999999988</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1008</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>10</v>
       </c>
       <c r="E230" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F230">
         <v>8862.31</v>
@@ -7197,7 +7198,7 @@
         <v>287489.4499999999</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1008</v>
       </c>
@@ -7211,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="E231" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F231">
         <v>0</v>
@@ -7226,7 +7227,7 @@
         <v>279195.95</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>1008</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F232">
         <v>0</v>
@@ -7255,7 +7256,7 @@
         <v>230392.75</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1008</v>
       </c>
@@ -7269,7 +7270,7 @@
         <v>13</v>
       </c>
       <c r="E233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F233">
         <v>0</v>
@@ -7284,7 +7285,7 @@
         <v>212814.07999999999</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>1008</v>
       </c>
@@ -7298,7 +7299,7 @@
         <v>19</v>
       </c>
       <c r="E234" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F234">
         <v>1588.85</v>
@@ -7313,7 +7314,7 @@
         <v>203024.9</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1008</v>
       </c>
@@ -7327,7 +7328,7 @@
         <v>11</v>
       </c>
       <c r="E235" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F235">
         <v>10242</v>
@@ -7342,7 +7343,7 @@
         <v>181159.96000000011</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1008</v>
       </c>
@@ -7356,7 +7357,7 @@
         <v>15</v>
       </c>
       <c r="E236" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F236">
         <v>0</v>
@@ -7371,7 +7372,7 @@
         <v>199366.60000000009</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1008</v>
       </c>
@@ -7385,7 +7386,7 @@
         <v>12</v>
       </c>
       <c r="E237" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -7400,7 +7401,7 @@
         <v>182768.84000000011</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1008</v>
       </c>
@@ -7414,7 +7415,7 @@
         <v>13</v>
       </c>
       <c r="E238" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F238">
         <v>0</v>
@@ -7429,7 +7430,7 @@
         <v>202704.31000000011</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1008</v>
       </c>
@@ -7443,7 +7444,7 @@
         <v>17</v>
       </c>
       <c r="E239" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F239">
         <v>0</v>
@@ -7458,7 +7459,7 @@
         <v>220697.67</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1008</v>
       </c>
@@ -7472,7 +7473,7 @@
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F240">
         <v>20223.16</v>
@@ -7487,7 +7488,7 @@
         <v>201685.57</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>1008</v>
       </c>
@@ -7501,7 +7502,7 @@
         <v>16</v>
       </c>
       <c r="E241" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F241">
         <v>18339.87</v>
@@ -7516,7 +7517,7 @@
         <v>190260.73</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1009</v>
       </c>
@@ -7530,7 +7531,7 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F242">
         <v>23133.45</v>
@@ -7545,7 +7546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1009</v>
       </c>
@@ -7559,7 +7560,7 @@
         <v>12</v>
       </c>
       <c r="E243" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -7574,7 +7575,7 @@
         <v>24519.439999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>1009</v>
       </c>
@@ -7588,7 +7589,7 @@
         <v>19</v>
       </c>
       <c r="E244" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F244">
         <v>5040.1000000000004</v>
@@ -7603,7 +7604,7 @@
         <v>100276.29</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1009</v>
       </c>
@@ -7617,7 +7618,7 @@
         <v>13</v>
       </c>
       <c r="E245" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F245">
         <v>23257.599999999999</v>
@@ -7632,7 +7633,7 @@
         <v>87008.63</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1009</v>
       </c>
@@ -7646,7 +7647,7 @@
         <v>12</v>
       </c>
       <c r="E246" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F246">
         <v>5442.05</v>
@@ -7661,7 +7662,7 @@
         <v>111108.54</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1009</v>
       </c>
@@ -7675,7 +7676,7 @@
         <v>12</v>
       </c>
       <c r="E247" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -7690,7 +7691,7 @@
         <v>140463.6</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1009</v>
       </c>
@@ -7704,7 +7705,7 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F248">
         <v>0</v>
@@ -7719,7 +7720,7 @@
         <v>120258.33</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1009</v>
       </c>
@@ -7733,7 +7734,7 @@
         <v>16</v>
       </c>
       <c r="E249" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F249">
         <v>0</v>
@@ -7748,7 +7749,7 @@
         <v>119142.96</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>1009</v>
       </c>
@@ -7762,7 +7763,7 @@
         <v>11</v>
       </c>
       <c r="E250" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F250">
         <v>0</v>
@@ -7777,7 +7778,7 @@
         <v>215147.75000000009</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>1009</v>
       </c>
@@ -7791,7 +7792,7 @@
         <v>13</v>
       </c>
       <c r="E251" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F251">
         <v>16304.4</v>
@@ -7806,7 +7807,7 @@
         <v>272128.34999999998</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>1009</v>
       </c>
@@ -7820,7 +7821,7 @@
         <v>13</v>
       </c>
       <c r="E252" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F252">
         <v>8943.0300000000007</v>
@@ -7835,7 +7836,7 @@
         <v>278499.28000000003</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1009</v>
       </c>
@@ -7849,7 +7850,7 @@
         <v>11</v>
       </c>
       <c r="E253" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F253">
         <v>23087.21</v>
@@ -7864,7 +7865,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1009</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F254">
         <v>8519.67</v>
@@ -7893,7 +7894,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1009</v>
       </c>
@@ -7907,7 +7908,7 @@
         <v>18</v>
       </c>
       <c r="E255" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F255">
         <v>2074.54</v>
@@ -7922,7 +7923,7 @@
         <v>296178.03999999998</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>1009</v>
       </c>
@@ -7936,7 +7937,7 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F256">
         <v>9483.7099999999991</v>
@@ -7951,7 +7952,7 @@
         <v>326280.03999999992</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>1009</v>
       </c>
@@ -7965,7 +7966,7 @@
         <v>13</v>
       </c>
       <c r="E257" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F257">
         <v>22176.63</v>
@@ -7980,7 +7981,7 @@
         <v>313589.22999999992</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>1009</v>
       </c>
@@ -7994,7 +7995,7 @@
         <v>13</v>
       </c>
       <c r="E258" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F258">
         <v>6162.04</v>
@@ -8009,7 +8010,7 @@
         <v>291634.41999999993</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>1009</v>
       </c>
@@ -8023,7 +8024,7 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F259">
         <v>18206.73</v>
@@ -8038,7 +8039,7 @@
         <v>287489.4499999999</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>1009</v>
       </c>
@@ -8052,7 +8053,7 @@
         <v>12</v>
       </c>
       <c r="E260" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F260">
         <v>0</v>
@@ -8067,7 +8068,7 @@
         <v>298472.87999999989</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1009</v>
       </c>
@@ -8081,7 +8082,7 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F261">
         <v>0</v>
@@ -8096,7 +8097,7 @@
         <v>261728</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>1009</v>
       </c>
@@ -8110,7 +8111,7 @@
         <v>19</v>
       </c>
       <c r="E262" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F262">
         <v>19239.849999999999</v>
@@ -8125,7 +8126,7 @@
         <v>243665.41</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1009</v>
       </c>
@@ -8139,7 +8140,7 @@
         <v>10</v>
       </c>
       <c r="E263" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F263">
         <v>13374.15</v>
@@ -8154,7 +8155,7 @@
         <v>230392.75</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1009</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>17</v>
       </c>
       <c r="E264" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F264">
         <v>0</v>
@@ -8183,7 +8184,7 @@
         <v>203024.9</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>1009</v>
       </c>
@@ -8197,7 +8198,7 @@
         <v>18</v>
       </c>
       <c r="E265" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F265">
         <v>4391.87</v>
@@ -8212,7 +8213,7 @@
         <v>203024.9</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1009</v>
       </c>
@@ -8226,7 +8227,7 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -8241,7 +8242,7 @@
         <v>186078.79</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>1009</v>
       </c>
@@ -8255,7 +8256,7 @@
         <v>17</v>
       </c>
       <c r="E267" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F267">
         <v>21058.7</v>
@@ -8270,7 +8271,7 @@
         <v>177837.53</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1009</v>
       </c>
@@ -8284,7 +8285,7 @@
         <v>13</v>
       </c>
       <c r="E268" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F268">
         <v>14708.44</v>
@@ -8299,7 +8300,7 @@
         <v>177837.53</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1009</v>
       </c>
@@ -8313,7 +8314,7 @@
         <v>16</v>
       </c>
       <c r="E269" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F269">
         <v>12107.83</v>
@@ -8328,7 +8329,7 @@
         <v>177837.53</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1009</v>
       </c>
@@ -8342,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F270">
         <v>0</v>
@@ -8357,7 +8358,7 @@
         <v>190260.73</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1009</v>
       </c>
@@ -8371,7 +8372,7 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F271">
         <v>24001.73</v>
@@ -8386,7 +8387,7 @@
         <v>190260.73</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1010</v>
       </c>
@@ -8400,7 +8401,7 @@
         <v>10</v>
       </c>
       <c r="E272" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F272">
         <v>19034.59</v>
@@ -8415,7 +8416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>1010</v>
       </c>
@@ -8429,7 +8430,7 @@
         <v>13</v>
       </c>
       <c r="E273" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F273">
         <v>0</v>
@@ -8444,7 +8445,7 @@
         <v>20248.509999999998</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>1010</v>
       </c>
@@ -8458,7 +8459,7 @@
         <v>16</v>
       </c>
       <c r="E274" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F274">
         <v>23783.54</v>
@@ -8473,7 +8474,7 @@
         <v>80902.360000000015</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>1010</v>
       </c>
@@ -8487,7 +8488,7 @@
         <v>10</v>
       </c>
       <c r="E275" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F275">
         <v>976.75</v>
@@ -8502,7 +8503,7 @@
         <v>121171.87</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>1010</v>
       </c>
@@ -8516,7 +8517,7 @@
         <v>16</v>
       </c>
       <c r="E276" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F276">
         <v>0</v>
@@ -8531,7 +8532,7 @@
         <v>136459.87</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1010</v>
       </c>
@@ -8545,7 +8546,7 @@
         <v>19</v>
       </c>
       <c r="E277" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F277">
         <v>0</v>
@@ -8560,7 +8561,7 @@
         <v>126470.07</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1010</v>
       </c>
@@ -8574,7 +8575,7 @@
         <v>12</v>
       </c>
       <c r="E278" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F278">
         <v>0</v>
@@ -8589,7 +8590,7 @@
         <v>137985.32</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1010</v>
       </c>
@@ -8603,7 +8604,7 @@
         <v>17</v>
       </c>
       <c r="E279" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F279">
         <v>16136.48</v>
@@ -8618,7 +8619,7 @@
         <v>119142.96</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1010</v>
       </c>
@@ -8632,7 +8633,7 @@
         <v>19</v>
       </c>
       <c r="E280" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F280">
         <v>15072.88</v>
@@ -8647,7 +8648,7 @@
         <v>169909.73</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>1010</v>
       </c>
@@ -8661,7 +8662,7 @@
         <v>15</v>
       </c>
       <c r="E281" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F281">
         <v>20128.34</v>
@@ -8676,7 +8677,7 @@
         <v>205077.78000000009</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1010</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F282">
         <v>5019.8999999999996</v>
@@ -8705,7 +8706,7 @@
         <v>278499.28000000003</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>1010</v>
       </c>
@@ -8719,7 +8720,7 @@
         <v>17</v>
       </c>
       <c r="E283" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F283">
         <v>0</v>
@@ -8734,7 +8735,7 @@
         <v>293999.39</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>1010</v>
       </c>
@@ -8748,7 +8749,7 @@
         <v>14</v>
       </c>
       <c r="E284" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -8763,7 +8764,7 @@
         <v>321403.08</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1010</v>
       </c>
@@ -8777,7 +8778,7 @@
         <v>18</v>
       </c>
       <c r="E285" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F285">
         <v>22211.24</v>
@@ -8792,7 +8793,7 @@
         <v>321403.08</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1010</v>
       </c>
@@ -8806,7 +8807,7 @@
         <v>15</v>
       </c>
       <c r="E286" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -8821,7 +8822,7 @@
         <v>322189.03999999998</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1010</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F287">
         <v>0</v>
@@ -8850,7 +8851,7 @@
         <v>304838.21000000002</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1010</v>
       </c>
@@ -8864,7 +8865,7 @@
         <v>12</v>
       </c>
       <c r="E288" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F288">
         <v>2766.52</v>
@@ -8879,7 +8880,7 @@
         <v>298472.87999999989</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>1010</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>17</v>
       </c>
       <c r="E289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F289">
         <v>0</v>
@@ -8908,7 +8909,7 @@
         <v>274424.47999999992</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1010</v>
       </c>
@@ -8922,7 +8923,7 @@
         <v>14</v>
       </c>
       <c r="E290" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F290">
         <v>17603.439999999999</v>
@@ -8937,7 +8938,7 @@
         <v>279195.95</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1010</v>
       </c>
@@ -8951,7 +8952,7 @@
         <v>19</v>
       </c>
       <c r="E291" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F291">
         <v>13524.06</v>
@@ -8966,7 +8967,7 @@
         <v>299242.35999999993</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1010</v>
       </c>
@@ -8980,7 +8981,7 @@
         <v>19</v>
       </c>
       <c r="E292" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F292">
         <v>0</v>
@@ -8995,7 +8996,7 @@
         <v>275034.07</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1010</v>
       </c>
@@ -9009,7 +9010,7 @@
         <v>17</v>
       </c>
       <c r="E293" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F293">
         <v>0</v>
@@ -9024,7 +9025,7 @@
         <v>243665.41</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1010</v>
       </c>
@@ -9038,7 +9039,7 @@
         <v>19</v>
       </c>
       <c r="E294" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -9053,7 +9054,7 @@
         <v>241012.55</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>1010</v>
       </c>
@@ -9067,7 +9068,7 @@
         <v>18</v>
       </c>
       <c r="E295" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F295">
         <v>13049.57</v>
@@ -9082,7 +9083,7 @@
         <v>241012.55</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1010</v>
       </c>
@@ -9096,7 +9097,7 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F296">
         <v>2163.04</v>
@@ -9111,7 +9112,7 @@
         <v>230392.75</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>1010</v>
       </c>
@@ -9125,7 +9126,7 @@
         <v>13</v>
       </c>
       <c r="E297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F297">
         <v>7465.31</v>
@@ -9140,7 +9141,7 @@
         <v>230392.75</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>1010</v>
       </c>
@@ -9154,7 +9155,7 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F298">
         <v>18300.25</v>
@@ -9169,7 +9170,7 @@
         <v>203024.9</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>1010</v>
       </c>
@@ -9183,7 +9184,7 @@
         <v>19</v>
       </c>
       <c r="E299" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -9198,7 +9199,7 @@
         <v>192360.84</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>1010</v>
       </c>
@@ -9212,7 +9213,7 @@
         <v>13</v>
       </c>
       <c r="E300" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F300">
         <v>24161.99</v>
@@ -9227,7 +9228,7 @@
         <v>170269.24</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>1010</v>
       </c>
@@ -9241,7 +9242,7 @@
         <v>16</v>
       </c>
       <c r="E301" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F301">
         <v>0</v>
@@ -9257,6 +9258,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I301" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1001"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>